--- a/data/trans_bre/P5_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P5_R-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,74; 9,95</t>
+          <t>-17,01; 9,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,14; 16,77</t>
+          <t>-25,06; 14,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,99; 11,1</t>
+          <t>-20,21; 11,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 1,42</t>
+          <t>-8,69; 1,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-52,44; 73,32</t>
+          <t>-55,11; 62,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,36; 59,55</t>
+          <t>-52,74; 49,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-45,42; 38,19</t>
+          <t>-44,74; 36,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,27; 7,68</t>
+          <t>-18,08; 6,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,09; 6,2</t>
+          <t>-22,82; 5,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,66; 7,02</t>
+          <t>-20,88; 3,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 55,52</t>
+          <t>3,23; 59,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,94; 36,11</t>
+          <t>-49,55; 30,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,08; 21,08</t>
+          <t>-52,97; 18,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,02; 13,26</t>
+          <t>-32,93; 7,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,98; 918,3</t>
+          <t>26,23; 1020,87</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 13,6</t>
+          <t>-11,39; 14,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 19,82</t>
+          <t>-10,57; 20,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,54; 8,99</t>
+          <t>-16,56; 10,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 13,62</t>
+          <t>-10,63; 12,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-34,01; 49,2</t>
+          <t>-29,99; 55,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,84; 51,53</t>
+          <t>-19,49; 52,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-48,47; 42,41</t>
+          <t>-45,7; 42,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-40,18; 88,51</t>
+          <t>-41,6; 85,32</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 13,02</t>
+          <t>-9,99; 12,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 20,96</t>
+          <t>-7,65; 21,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-17,74; 15,9</t>
+          <t>-18,32; 16,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 13,03</t>
+          <t>-9,26; 12,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,53; 69,62</t>
+          <t>-34,72; 72,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,33; 122,25</t>
+          <t>-26,96; 117,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-41,65; 66,77</t>
+          <t>-44,04; 64,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,2; 166,76</t>
+          <t>-46,62; 164,02</t>
         </is>
       </c>
     </row>
@@ -1060,37 +1060,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 55,42</t>
+          <t>-10,05; 58,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 31,14</t>
+          <t>-20,99; 30,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-26,42; 10,72</t>
+          <t>-25,28; 8,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 5,09</t>
+          <t>-3,2; 5,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,21; 285,94</t>
+          <t>-18,28; 313,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,21; 63,94</t>
+          <t>-28,28; 62,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-54,66; 34,48</t>
+          <t>-53,89; 30,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,49 +1160,49 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 15,56</t>
+          <t>-7,55; 15,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,7; 12,79</t>
+          <t>-24,3; 12,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-25,19; 18,82</t>
+          <t>-23,83; 21,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 20,68</t>
+          <t>-4,12; 19,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-45,06; 219,75</t>
+          <t>-47,15; 205,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-38,75; 29,47</t>
+          <t>-40,97; 30,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-47,14; 62,96</t>
+          <t>-46,18; 76,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,58; 215,91</t>
+          <t>-23,23; 229,99</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 10,51</t>
+          <t>-8,47; 10,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 11,62</t>
+          <t>-9,14; 11,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 9,19</t>
+          <t>-10,6; 9,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 9,82</t>
+          <t>-12,96; 8,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-26,84; 49,81</t>
+          <t>-26,55; 50,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,0; 29,69</t>
+          <t>-18,53; 27,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-26,2; 28,81</t>
+          <t>-25,25; 30,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-29,81; 34,25</t>
+          <t>-30,54; 28,14</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 9,15</t>
+          <t>-13,56; 9,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 8,72</t>
+          <t>-8,99; 8,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 11,11</t>
+          <t>-6,33; 11,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 7,66</t>
+          <t>-6,7; 7,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,41; 28,3</t>
+          <t>-31,25; 28,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,69; 42,09</t>
+          <t>-31,92; 44,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 47,64</t>
+          <t>-19,65; 43,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-37,1; 69,08</t>
+          <t>-37,52; 67,15</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 4,42</t>
+          <t>-4,46; 4,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 4,99</t>
+          <t>-5,31; 4,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 2,74</t>
+          <t>-6,96; 2,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 15,42</t>
+          <t>-0,52; 14,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 17,42</t>
+          <t>-14,53; 17,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 14,08</t>
+          <t>-12,94; 13,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-17,94; 7,8</t>
+          <t>-17,8; 6,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 94,72</t>
+          <t>-3,43; 93,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P5_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P5_R-Provincia-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 9,6</t>
+          <t>-16,75; 11,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 14,15</t>
+          <t>-24,26; 14,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,21; 11,13</t>
+          <t>-20,48; 11,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 1,76</t>
+          <t>-9,1; 1,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-55,11; 62,14</t>
+          <t>-56,58; 77,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-52,74; 49,05</t>
+          <t>-51,48; 47,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-44,74; 36,13</t>
+          <t>-44,54; 38,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 6,63</t>
+          <t>-17,21; 7,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,82; 5,09</t>
+          <t>-22,58; 4,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,88; 3,97</t>
+          <t>-22,05; 6,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 59,67</t>
+          <t>2,69; 62,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,55; 30,98</t>
+          <t>-48,61; 31,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,97; 18,14</t>
+          <t>-50,47; 20,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-32,93; 7,32</t>
+          <t>-33,48; 12,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,23; 1020,87</t>
+          <t>22,63; 1061,69</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 14,1</t>
+          <t>-11,66; 13,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 20,79</t>
+          <t>-10,83; 20,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 10,28</t>
+          <t>-16,45; 10,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 12,12</t>
+          <t>-10,6; 12,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-29,99; 55,41</t>
+          <t>-30,74; 53,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,49; 52,44</t>
+          <t>-19,42; 53,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-45,7; 42,43</t>
+          <t>-47,84; 48,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-41,6; 85,32</t>
+          <t>-41,25; 78,99</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 12,96</t>
+          <t>-11,83; 11,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 21,66</t>
+          <t>-9,98; 19,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 16,18</t>
+          <t>-19,31; 14,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 12,71</t>
+          <t>-10,12; 12,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,72; 72,81</t>
+          <t>-40,18; 72,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,96; 117,87</t>
+          <t>-30,08; 110,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-44,04; 64,08</t>
+          <t>-45,26; 54,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,62; 164,02</t>
+          <t>-50,99; 154,65</t>
         </is>
       </c>
     </row>
@@ -1060,37 +1060,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 58,79</t>
+          <t>-10,5; 56,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,99; 30,89</t>
+          <t>-18,98; 31,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,28; 8,84</t>
+          <t>-25,49; 10,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 5,02</t>
+          <t>-3,15; 5,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 313,41</t>
+          <t>-19,89; 322,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,28; 62,23</t>
+          <t>-26,81; 63,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-53,89; 30,0</t>
+          <t>-54,85; 32,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 15,39</t>
+          <t>-7,26; 15,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-24,3; 12,27</t>
+          <t>-23,52; 10,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 21,62</t>
+          <t>-20,44; 21,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 19,97</t>
+          <t>-3,17; 20,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,15; 205,17</t>
+          <t>-44,97; 213,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,97; 30,35</t>
+          <t>-40,61; 24,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-46,18; 76,8</t>
+          <t>-41,78; 76,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,23; 229,99</t>
+          <t>-20,6; 208,76</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 10,94</t>
+          <t>-9,65; 10,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 11,12</t>
+          <t>-9,89; 11,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 9,6</t>
+          <t>-10,49; 9,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 8,57</t>
+          <t>-12,0; 9,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-26,55; 50,5</t>
+          <t>-31,62; 47,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 27,91</t>
+          <t>-19,87; 27,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-25,25; 30,23</t>
+          <t>-24,82; 29,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-30,54; 28,14</t>
+          <t>-28,46; 31,86</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 9,38</t>
+          <t>-13,93; 10,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 8,98</t>
+          <t>-9,37; 10,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 11,12</t>
+          <t>-6,39; 11,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 7,33</t>
+          <t>-7,07; 7,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,25; 28,86</t>
+          <t>-31,17; 31,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-31,92; 44,1</t>
+          <t>-33,35; 54,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 43,08</t>
+          <t>-19,93; 44,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-37,52; 67,15</t>
+          <t>-40,22; 62,51</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 4,56</t>
+          <t>-4,13; 4,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 4,87</t>
+          <t>-5,29; 4,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 2,36</t>
+          <t>-7,73; 2,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 14,4</t>
+          <t>-0,59; 14,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 17,81</t>
+          <t>-13,9; 17,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 13,67</t>
+          <t>-12,98; 12,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 6,8</t>
+          <t>-18,99; 6,08</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 93,96</t>
+          <t>-3,99; 92,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P5_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P5_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,33</t>
+          <t>-1,86</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-57,13%</t>
+          <t>-48,35%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 11,15</t>
+          <t>-15,74; 9,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,26; 14,93</t>
+          <t>-24,14; 16,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,48; 11,6</t>
+          <t>-20,99; 11,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 1,54</t>
+          <t>-7,01; 2,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-56,58; 77,42</t>
+          <t>-52,44; 73,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 47,73</t>
+          <t>-48,36; 59,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-44,54; 38,94</t>
+          <t>-45,42; 38,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22,93</t>
+          <t>7,97</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>218,2%</t>
+          <t>76,96%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,21; 7,44</t>
+          <t>-17,27; 7,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,58; 4,91</t>
+          <t>-23,09; 6,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,05; 6,41</t>
+          <t>-20,66; 7,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 62,13</t>
+          <t>0,45; 18,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,61; 31,62</t>
+          <t>-45,94; 36,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-50,47; 20,23</t>
+          <t>-52,08; 21,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,48; 12,55</t>
+          <t>-33,02; 13,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,63; 1061,69</t>
+          <t>-4,96; 272,46</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 13,85</t>
+          <t>-12,32; 13,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 20,61</t>
+          <t>-10,16; 19,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 10,62</t>
+          <t>-17,54; 8,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 12,24</t>
+          <t>-10,92; 12,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-30,74; 53,95</t>
+          <t>-34,01; 49,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 53,65</t>
+          <t>-18,84; 51,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-47,84; 48,41</t>
+          <t>-48,47; 42,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-41,25; 78,99</t>
+          <t>-42,42; 81,95</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 11,82</t>
+          <t>-9,64; 13,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 19,83</t>
+          <t>-9,33; 20,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,31; 14,46</t>
+          <t>-17,74; 15,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 12,87</t>
+          <t>-12,51; 12,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,18; 72,2</t>
+          <t>-34,53; 69,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,08; 110,86</t>
+          <t>-28,33; 122,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,26; 54,39</t>
+          <t>-41,65; 66,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,99; 154,65</t>
+          <t>-55,27; 149,88</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -1060,37 +1060,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 56,06</t>
+          <t>-9,85; 55,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,98; 31,05</t>
+          <t>-17,85; 31,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,49; 10,11</t>
+          <t>-26,42; 10,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 5,07</t>
+          <t>-3,31; 5,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,89; 322,07</t>
+          <t>-18,21; 285,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,81; 63,47</t>
+          <t>-25,21; 63,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-54,85; 32,76</t>
+          <t>-54,66; 34,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,4</t>
+          <t>7,8</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>53,11%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 15,61</t>
+          <t>-7,19; 15,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,52; 10,16</t>
+          <t>-22,7; 12,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,44; 21,22</t>
+          <t>-25,19; 18,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 20,69</t>
+          <t>-6,21; 19,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-44,97; 213,3</t>
+          <t>-45,06; 219,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,61; 24,47</t>
+          <t>-38,75; 29,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,78; 76,43</t>
+          <t>-47,14; 62,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,6; 208,76</t>
+          <t>-30,67; 201,84</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,88</t>
+          <t>-3,82</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-5,11%</t>
+          <t>-9,93%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 10,72</t>
+          <t>-8,01; 10,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 11,13</t>
+          <t>-9,32; 11,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 9,2</t>
+          <t>-11,31; 9,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 9,83</t>
+          <t>-13,89; 6,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-31,62; 47,66</t>
+          <t>-26,84; 49,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 27,03</t>
+          <t>-19,0; 29,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-24,82; 29,61</t>
+          <t>-26,2; 28,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-28,46; 31,86</t>
+          <t>-32,92; 21,52</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 10,15</t>
+          <t>-13,71; 9,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 10,08</t>
+          <t>-8,63; 8,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 11,0</t>
+          <t>-6,68; 11,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 7,31</t>
+          <t>-6,05; 7,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,17; 31,84</t>
+          <t>-31,41; 28,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-33,35; 54,01</t>
+          <t>-30,69; 42,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,93; 44,8</t>
+          <t>-20,34; 47,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-40,22; 62,51</t>
+          <t>-37,15; 70,26</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,11</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 4,53</t>
+          <t>-4,22; 4,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 4,48</t>
+          <t>-5,4; 4,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 2,14</t>
+          <t>-7,02; 2,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 14,73</t>
+          <t>-2,68; 4,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 17,33</t>
+          <t>-14,08; 17,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 12,29</t>
+          <t>-12,86; 14,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 6,08</t>
+          <t>-17,94; 7,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 92,1</t>
+          <t>-14,1; 30,7</t>
         </is>
       </c>
     </row>
